--- a/data/S1990_91_FINAL.xlsx
+++ b/data/S1990_91_FINAL.xlsx
@@ -27,8 +27,11 @@
     <sheet name="SERIES" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="CLUBS" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="META" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -36,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,8 +54,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +81,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -87,12 +99,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -22752,7 +22770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22796,6 +22814,98 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1990_91_0082 'TJ Slezan Frýdek-Místek' prev→CLUB_S1989_90_0455 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1990_91_0098 'TJ Slovan OSCR Topoľčany' prev→CLUB_S1989_90_0096 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0018</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1990_91_0018 'Prolínací soutěž' (L15, parent=NODE_S1990_91_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1990_91_0026 'Kvalifikace o 2. ČNHL' (L25, parent=NODE_S1990_91_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0027</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1990_91_0027 'Kvalifikace o 2. ČNHL skupina A' (L25, parent=NODE_S1990_91_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0028</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1990_91_0028 'Kvalifikace o 2. ČNHL skupina B' (L25, parent=NODE_S1990_91_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -27787,8 +27897,6 @@
         </is>
       </c>
     </row>
-    <row r="118"/>
-    <row r="119"/>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
@@ -27868,7 +27976,6 @@
         </is>
       </c>
     </row>
-    <row r="127"/>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
@@ -56421,6 +56528,193 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0082</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0082 'TJ Slezan Frýdek-Místek' prev→CLUB_S1989_90_0455 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0098</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0098 'TJ Slovan OSCR Topoľčany' prev→CLUB_S1989_90_0096 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0018</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1990_91_0018 'Prolínací soutěž' (L15, parent=NODE_S1990_91_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0026</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1990_91_0026 'Kvalifikace o 2. ČNHL' (L25, parent=NODE_S1990_91_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0027</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1990_91_0027 'Kvalifikace o 2. ČNHL skupina A' (L25, parent=NODE_S1990_91_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0028</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1990_91_0028 'Kvalifikace o 2. ČNHL skupina B' (L25, parent=NODE_S1990_91_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1990_91_FINAL.xlsx
+++ b/data/S1990_91_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22770,7 +22770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22820,7 +22820,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1990_91_0082 'TJ Slezan Frýdek-Místek' prev→CLUB_S1989_90_0455 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -22832,7 +22832,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1990_91_0098 'TJ Slovan OSCR Topoľčany' prev→CLUB_S1989_90_0096 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -22842,14 +22842,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NODE_S1990_91_0018</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1990_91_0018 'Prolínací soutěž' (L15, parent=NODE_S1990_91_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -22859,14 +22854,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S1990_91_0026</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1990_91_0026 'Kvalifikace o 2. ČNHL' (L25, parent=NODE_S1990_91_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -22876,14 +22866,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NODE_S1990_91_0027</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1990_91_0027 'Kvalifikace o 2. ČNHL skupina A' (L25, parent=NODE_S1990_91_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -22893,17 +22878,576 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NODE_S1990_91_0028</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1990_91_0028 'Kvalifikace o 2. ČNHL skupina B' (L25, parent=NODE_S1990_91_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ÚDDM Praha' → 'Praha jih' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0455 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0096 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0122 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0166 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0365 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'OS VB Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Státní Statek Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -27897,6 +28441,8 @@
         </is>
       </c>
     </row>
+    <row r="118"/>
+    <row r="119"/>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
@@ -27927,6 +28473,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0001</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -27939,6 +28490,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0003</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -27951,6 +28507,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0003</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -27963,6 +28524,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0035</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -27976,6 +28542,7 @@
         </is>
       </c>
     </row>
+    <row r="127"/>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
@@ -29500,12 +30067,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -29631,12 +30198,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -29673,12 +30240,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -29715,12 +30282,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -30187,12 +30754,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -30229,12 +30796,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -30402,12 +30969,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom.</t>
+          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom. || TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>SMZ Dubnica nad Váhom</t>
+          <t>Dubnica nad Váhom</t>
         </is>
       </c>
     </row>
@@ -31002,12 +31569,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Praha = TJ ÚDDM Praha (Wiki D42 - registr ustavy 04/2026). **ÚDDM** = Ústřední dům dětí a mládeže (drive ÚDPM). city Praha.</t>
+          <t>Praha = TJ ÚDDM Praha (Wiki D42 - registr ustavy 04/2026). **ÚDDM** = Ústřední dům dětí a mládeže (drive ÚDPM). city Praha. || TBD: city 'ÚDDM Praha' → 'Praha jih' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>ÚDDM Praha</t>
+          <t>Praha jih</t>
         </is>
       </c>
     </row>
@@ -31590,12 +32157,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -31679,12 +32246,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -31721,12 +32288,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -31805,12 +32372,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha.</t>
+          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha. || TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>DP I. ČLTK Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -32366,12 +32933,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov.</t>
+          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov. || TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>VVŠ PV Vyškov</t>
+          <t>Vyškov</t>
         </is>
       </c>
     </row>
@@ -32408,12 +32975,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -32707,12 +33274,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Piešťany = HK Chirana Piešťany (Wiki D42 - registr ustavy 04/2026). Slovensky/Trnavsky kraj. city Piešťany.</t>
+          <t>Piešťany = HK Chirana Piešťany (Wiki D42 - registr ustavy 04/2026). Slovensky/Trnavsky kraj. city Piešťany. || TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>HK Chirana Piešťany</t>
+          <t>Chirana Piešťany</t>
         </is>
       </c>
     </row>
@@ -32880,12 +33447,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Nové Zámky = TJ Lokomotiva Nové Zámky (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. Železničárský klub. Patterns: Lokomotíva Nové Zámky -&gt; Lokomotiva Nové Zámky. city Nové Zámky.</t>
+          <t>Nové Zámky = TJ Lokomotiva Nové Zámky (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. Železničárský klub. Patterns: Lokomotíva Nové Zámky -&gt; Lokomotiva Nové Zámky. city Nové Zámky. || TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Lokomotiva Nové Zámky</t>
+          <t>Nové Zámky</t>
         </is>
       </c>
     </row>
@@ -34207,12 +34774,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr.</t>
+          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr. || TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>KŽ Králův Dvůr</t>
+          <t>Králův Dvůr</t>
         </is>
       </c>
     </row>
@@ -37609,12 +38176,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -37651,12 +38218,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -38257,12 +38824,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -38346,12 +38913,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -38393,12 +38960,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -38576,12 +39143,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -38670,12 +39237,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -38759,12 +39326,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -38853,12 +39420,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -40668,12 +41235,12 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu.</t>
+          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu. || TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Start VD Luby</t>
+          <t>Luby</t>
         </is>
       </c>
     </row>
@@ -42020,14 +42587,9 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H301" t="inlineStr">
-        <is>
-          <t>CLUB_S1989_90_0083</t>
-        </is>
-      </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice.</t>
+          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
@@ -42106,12 +42668,12 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -42148,12 +42710,12 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou. || TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>Bižuterie Jablonec</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -42321,12 +42883,12 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -42670,14 +43232,9 @@
           <t>skupina A</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>CLUB_S1989_90_0083</t>
-        </is>
-      </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice.</t>
+          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
@@ -42927,14 +43484,9 @@
           <t>skupina A</t>
         </is>
       </c>
-      <c r="H322" t="inlineStr">
-        <is>
-          <t>CLUB_S1989_90_0083</t>
-        </is>
-      </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice.</t>
+          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
@@ -44236,12 +44788,12 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov.</t>
+          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov. || TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>Tepna ČKD Hronov</t>
+          <t>Hronov</t>
         </is>
       </c>
     </row>
@@ -45882,12 +46434,12 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>Pardubice = TJ OS VB Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **OS VB** = Okresni sprava verejne bezpecnosti (policie). city Pardubice.</t>
+          <t>Pardubice = TJ OS VB Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **OS VB** = Okresni sprava verejne bezpecnosti (policie). city Pardubice. || TBD: city 'OS VB Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>OS VB Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
     </row>
@@ -46097,12 +46649,12 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>Pardubice = TJ Státní Statek Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. city Pardubice.</t>
+          <t>Pardubice = TJ Státní Statek Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. city Pardubice. || TBD: city 'Státní Statek Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>Státní Statek Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
     </row>
@@ -47184,12 +47736,12 @@
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -51376,12 +51928,12 @@
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t>Frenštát pod Radhoštěm = TJ MEZ Frenštát (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). **MEZ Frenštát** = Moravské elektrotechnické závody (pobocka). city Frenštát pod Radhoštěm.</t>
+          <t>Frenštát pod Radhoštěm = TJ MEZ Frenštát (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). **MEZ Frenštát** = Moravské elektrotechnické závody (pobocka). city Frenštát pod Radhoštěm. || TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>MEZ Frenštát</t>
+          <t>Frenštát pod Radhoštěm</t>
         </is>
       </c>
     </row>
@@ -51465,12 +52017,12 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -56534,11 +57086,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -56583,21 +57135,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0082</t>
+          <t>CLUB_S1990_91_0014</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0082 'TJ Slezan Frýdek-Místek' prev→CLUB_S1989_90_0455 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -56605,21 +57155,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0098</t>
+          <t>CLUB_S1990_91_0017</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0098 'TJ Slovan OSCR Topoľčany' prev→CLUB_S1989_90_0096 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -56627,21 +57175,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S1990_91_0018</t>
+          <t>CLUB_S1990_91_0018</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1990_91_0018 'Prolínací soutěž' (L15, parent=NODE_S1990_91_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -56649,21 +57195,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S1990_91_0026</t>
+          <t>CLUB_S1990_91_0019</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1990_91_0026 'Kvalifikace o 2. ČNHL' (L25, parent=NODE_S1990_91_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -56671,21 +57215,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NODE_S1990_91_0027</t>
+          <t>CLUB_S1990_91_0030</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1990_91_0027 'Kvalifikace o 2. ČNHL skupina A' (L25, parent=NODE_S1990_91_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -56693,24 +57235,962 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NODE_S1990_91_0028</t>
+          <t>CLUB_S1990_91_0031</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1990_91_0028 'Kvalifikace o 2. ČNHL skupina B' (L25, parent=NODE_S1990_91_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0035</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0052</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'ÚDDM Praha' → 'Praha jih' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0063</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0067</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0069</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0070</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0072</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0081</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0082</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0455 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0085</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0086</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0093</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0097</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0098</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0096 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0128</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0174</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0122 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0190</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0166 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0205</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0205</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0206</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0219</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0221</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0222</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0226</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0228</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0230</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0232</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0273</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0306</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0308</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0309</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0314</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0322</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0328</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0345</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0360</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0363</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0374</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0382</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0365 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0398</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'OS VB Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0403</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Státní Statek Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0414</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0430</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0433</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0436</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0529</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CLUB_S1990_91_0531</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7"/>
+  <autoFilter ref="A1:F54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -80844,11 +82324,6 @@
           <t>CLUB_S1990_91_0306</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>CLUB_S1989_90_0083</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>reorganizace</t>
@@ -81504,11 +82979,6 @@
           <t>CLUB_S1990_91_0306</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>CLUB_S1989_90_0083</t>
-        </is>
-      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>reorganizace</t>
@@ -82427,11 +83897,7 @@
           <t>CLUB_S1990_91_0322</t>
         </is>
       </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1989_90_0083</t>
-        </is>
-      </c>
+      <c r="R29" s="3" t="n"/>
       <c r="S29" s="3" t="n"/>
       <c r="T29" s="3" t="n"/>
       <c r="U29" s="3" t="n"/>
@@ -82701,11 +84167,7 @@
           <t>CLUB_S1990_91_0328</t>
         </is>
       </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1989_90_0083</t>
-        </is>
-      </c>
+      <c r="R35" s="3" t="n"/>
       <c r="S35" s="3" t="n"/>
       <c r="T35" s="3" t="n"/>
       <c r="U35" s="3" t="n"/>

--- a/data/S1990_91_FINAL.xlsx
+++ b/data/S1990_91_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22770,7 +22770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22820,7 +22820,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -22832,7 +22832,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -22844,7 +22844,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -22856,7 +22856,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -22868,7 +22868,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -22880,7 +22880,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -22892,7 +22892,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -22904,7 +22904,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'ÚDDM Praha' → 'Praha jih' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -22916,7 +22916,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -22928,7 +22928,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0455 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -22940,7 +22940,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -22952,7 +22952,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -22964,7 +22964,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -22976,7 +22976,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -22988,7 +22988,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0455 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0096 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -23000,7 +23000,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -23012,7 +23012,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0122 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -23024,7 +23024,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0166 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -23036,7 +23036,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -23048,7 +23048,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0096 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -23060,7 +23060,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -23072,7 +23072,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0122 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -23084,7 +23084,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0166 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -23096,7 +23096,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -23108,7 +23108,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -23120,7 +23120,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -23132,7 +23132,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -23144,7 +23144,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -23156,7 +23156,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -23168,7 +23168,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -23180,7 +23180,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -23192,7 +23192,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -23204,7 +23204,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -23216,7 +23216,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -23228,7 +23228,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0365 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -23240,7 +23240,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'OS VB Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -23252,7 +23252,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Státní Statek Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -23264,7 +23264,7 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -23276,7 +23276,7 @@
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -23288,7 +23288,7 @@
     <row r="42">
       <c r="C42" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -23300,7 +23300,7 @@
     <row r="43">
       <c r="C43" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -23312,142 +23312,10 @@
     <row r="44">
       <c r="C44" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0365 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'OS VB Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Státní Statek Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -23464,7 +23332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K132"/>
+  <dimension ref="A1:L132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23523,6 +23391,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23565,6 +23438,11 @@
           <t>14 týmů: základ + playoff (SF/finále/O 3.) Mistr: Dukla Jihlava.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23612,6 +23490,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23654,6 +23537,11 @@
           <t>I.ČNHL: základ + playoff (QF/SF/finále/O 3.) + O 5.-8. + o udržení. I.SNHL (12). Kval o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23696,6 +23584,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23780,6 +23673,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23822,6 +23720,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23864,6 +23767,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23906,6 +23814,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23948,6 +23861,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -23990,6 +23908,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24032,6 +23955,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24074,6 +24002,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24116,6 +24049,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24158,6 +24096,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24200,6 +24143,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24242,6 +24190,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -24284,6 +24237,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -24373,6 +24331,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -24415,6 +24378,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -24504,6 +24472,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -24546,6 +24519,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -24766,6 +24744,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0030</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -25018,6 +25001,11 @@
           <t>II.ČNHL: 3 skupiny + finále.</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0037</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -25060,6 +25048,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0038</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -25102,6 +25095,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0039</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -25144,6 +25142,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0040</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -25270,6 +25273,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0041</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -25438,6 +25446,11 @@
           <t>Skupina A + skupina B, semifinále, O 3. místo a finále.</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0043</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -25663,6 +25676,11 @@
           <t>V play-off je první utkání hráno doma.</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0053</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -25705,6 +25723,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0054</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -25747,6 +25770,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0055</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -25831,6 +25859,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0056</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -25873,6 +25906,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0057</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -25915,6 +25953,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0058</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -25957,6 +26000,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0059</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -25999,6 +26047,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0060</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -26041,6 +26094,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0061</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -26083,6 +26141,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0062</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -26125,6 +26188,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0064</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -26167,6 +26235,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0065</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -26209,6 +26282,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0066</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -26377,6 +26455,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0068</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -26419,6 +26502,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0069</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -26718,6 +26806,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0073</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -26760,6 +26853,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0074</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -26802,6 +26900,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0075</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -26844,6 +26947,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0076</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -26886,6 +26994,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0077</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -26928,6 +27041,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0079</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -27138,6 +27256,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0085</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -27180,6 +27303,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0086</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -27222,6 +27350,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0087</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -27264,6 +27397,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0088</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -27306,6 +27444,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0089</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -27432,6 +27575,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0093</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -27474,6 +27622,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0094</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -27516,6 +27669,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0095</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -27558,6 +27716,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0096</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -27600,6 +27763,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0097</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -27684,6 +27852,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0099</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -27726,6 +27899,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0100</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -27768,6 +27946,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0101</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -27810,6 +27993,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0102</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -27852,6 +28040,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0104</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -27894,6 +28087,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0105</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -27936,6 +28134,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0106</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -27978,6 +28181,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0107</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -28062,6 +28270,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0108</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -28104,6 +28317,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0109</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -28146,6 +28364,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0110</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -28188,6 +28411,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0111</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -28314,6 +28542,11 @@
           <t>Paralelní slovenské krajské registry; nejde o vertikální kaskádu.</t>
         </is>
       </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0114</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -28356,6 +28589,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0115</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -28398,6 +28636,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0116</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -28438,6 +28681,11 @@
       <c r="J117" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>NODE_S1989_90_0117</t>
         </is>
       </c>
     </row>
@@ -28461,6 +28709,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -28478,6 +28731,11 @@
           <t>NODE_S1990_91_0001</t>
         </is>
       </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -28495,6 +28753,11 @@
           <t>NODE_S1990_91_0003</t>
         </is>
       </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -28512,6 +28775,11 @@
           <t>NODE_S1990_91_0003</t>
         </is>
       </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -28529,6 +28797,11 @@
           <t>NODE_S1990_91_0035</t>
         </is>
       </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -28539,6 +28812,11 @@
       <c r="B126" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -30067,12 +30345,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -30198,12 +30476,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -30282,12 +30560,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Slezan Opava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -30796,12 +31074,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -31569,12 +31847,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Praha = TJ ÚDDM Praha (Wiki D42 - registr ustavy 04/2026). **ÚDDM** = Ústřední dům dětí a mládeže (drive ÚDPM). city Praha. || TBD: city 'ÚDDM Praha' → 'Praha jih' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Praha = TJ ÚDDM Praha (Wiki D42 - registr ustavy 04/2026). **ÚDDM** = Ústřední dům dětí a mládeže (drive ÚDPM). city Praha.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Praha jih</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -38176,12 +38454,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -38218,12 +38496,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -38824,12 +39102,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -38913,12 +39191,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -38960,12 +39238,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -52017,12 +52295,12 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -57086,7 +57364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -57140,12 +57418,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0014</t>
+          <t>CLUB_S1990_91_0018</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57160,12 +57438,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0017</t>
+          <t>CLUB_S1990_91_0030</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57180,12 +57458,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0018</t>
+          <t>CLUB_S1990_91_0035</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57200,12 +57478,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0019</t>
+          <t>CLUB_S1990_91_0063</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -57220,12 +57498,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0030</t>
+          <t>CLUB_S1990_91_0067</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57240,12 +57518,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0031</t>
+          <t>CLUB_S1990_91_0069</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57260,12 +57538,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0035</t>
+          <t>CLUB_S1990_91_0070</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57280,12 +57558,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0052</t>
+          <t>CLUB_S1990_91_0072</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'ÚDDM Praha' → 'Praha jih' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57300,12 +57578,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0063</t>
+          <t>CLUB_S1990_91_0081</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
     </row>
@@ -57320,12 +57598,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0067</t>
+          <t>CLUB_S1990_91_0082</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0455 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -57340,12 +57618,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0069</t>
+          <t>CLUB_S1990_91_0085</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57360,12 +57638,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0070</t>
+          <t>CLUB_S1990_91_0086</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57380,12 +57658,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0072</t>
+          <t>CLUB_S1990_91_0093</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57400,12 +57678,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0081</t>
+          <t>CLUB_S1990_91_0097</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57420,12 +57698,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0082</t>
+          <t>CLUB_S1990_91_0098</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0455 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0096 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -57440,12 +57718,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0085</t>
+          <t>CLUB_S1990_91_0128</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57460,12 +57738,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0086</t>
+          <t>CLUB_S1990_91_0174</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0122 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -57480,12 +57758,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0093</t>
+          <t>CLUB_S1990_91_0190</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0166 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -57500,12 +57778,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0097</t>
+          <t>CLUB_S1990_91_0205</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57520,12 +57798,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0098</t>
+          <t>CLUB_S1990_91_0226</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0096 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57540,12 +57818,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0128</t>
+          <t>CLUB_S1990_91_0228</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57560,12 +57838,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0174</t>
+          <t>CLUB_S1990_91_0230</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0122 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57580,12 +57858,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0190</t>
+          <t>CLUB_S1990_91_0232</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0166 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57600,12 +57878,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0205</t>
+          <t>CLUB_S1990_91_0273</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57620,12 +57898,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0205</t>
+          <t>CLUB_S1990_91_0306</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57640,12 +57918,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0206</t>
+          <t>CLUB_S1990_91_0308</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57660,12 +57938,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0219</t>
+          <t>CLUB_S1990_91_0309</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57680,12 +57958,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0221</t>
+          <t>CLUB_S1990_91_0314</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57700,12 +57978,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0222</t>
+          <t>CLUB_S1990_91_0322</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57720,12 +57998,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0226</t>
+          <t>CLUB_S1990_91_0328</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57740,12 +58018,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0228</t>
+          <t>CLUB_S1990_91_0345</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -57760,12 +58038,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0230</t>
+          <t>CLUB_S1990_91_0360</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57780,12 +58058,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0232</t>
+          <t>CLUB_S1990_91_0363</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -57800,12 +58078,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0273</t>
+          <t>CLUB_S1990_91_0374</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -57820,12 +58098,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0306</t>
+          <t>CLUB_S1990_91_0382</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0365 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -57840,12 +58118,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0308</t>
+          <t>CLUB_S1990_91_0398</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'OS VB Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57860,12 +58138,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0309</t>
+          <t>CLUB_S1990_91_0403</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Státní Statek Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57880,12 +58158,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0314</t>
+          <t>CLUB_S1990_91_0414</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
     </row>
@@ -57900,12 +58178,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0322</t>
+          <t>CLUB_S1990_91_0430</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57920,12 +58198,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0328</t>
+          <t>CLUB_S1990_91_0433</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -57940,12 +58218,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0345</t>
+          <t>CLUB_S1990_91_0436</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
     </row>
@@ -57960,237 +58238,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CLUB_S1990_91_0360</t>
+          <t>CLUB_S1990_91_0529</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CLUB_S1990_91_0363</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>CLUB_S1990_91_0374</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CLUB_S1990_91_0382</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1989_90_0365 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>CLUB_S1990_91_0398</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'OS VB Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>CLUB_S1990_91_0403</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Státní Statek Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CLUB_S1990_91_0414</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>CLUB_S1990_91_0430</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>CLUB_S1990_91_0433</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>CLUB_S1990_91_0436</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>CLUB_S1990_91_0529</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
           <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>CLUB_S1990_91_0531</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F54"/>
+  <autoFilter ref="A1:F43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1990_91_FINAL.xlsx
+++ b/data/S1990_91_FINAL.xlsx
@@ -54335,7 +54335,7 @@
         <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
         <v>100</v>
@@ -55329,7 +55329,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="M23" t="n">
         <v>50</v>
@@ -56178,7 +56178,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M35" t="n">
         <v>74</v>
@@ -56960,7 +56960,7 @@
         <v>31</v>
       </c>
       <c r="J45" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>

--- a/data/S1990_91_FINAL.xlsx
+++ b/data/S1990_91_FINAL.xlsx
@@ -23332,7 +23332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L132"/>
+  <dimension ref="A1:N132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23396,6 +23396,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28689,8 +28699,6 @@
         </is>
       </c>
     </row>
-    <row r="118"/>
-    <row r="119"/>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
@@ -28820,7 +28828,6 @@
         </is>
       </c>
     </row>
-    <row r="127"/>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>

--- a/data/S1990_91_FINAL.xlsx
+++ b/data/S1990_91_FINAL.xlsx
@@ -23673,6 +23673,16 @@
           <t>NODE_S1990_91_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0008</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0014</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23687,6 +23697,14 @@
         <is>
           <t>NODE_S1989_90_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -23767,6 +23785,16 @@
           <t>NODE_S1990_91_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0009</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0017</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23781,6 +23809,14 @@
         <is>
           <t>NODE_S1989_90_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -23814,6 +23850,16 @@
           <t>NODE_S1990_91_0007</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0013</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0012</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23828,6 +23874,14 @@
         <is>
           <t>NODE_S1989_90_0009</t>
         </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -23861,6 +23915,8 @@
           <t>NODE_S1990_91_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23875,6 +23931,14 @@
         <is>
           <t>NODE_S1989_90_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -23908,6 +23972,8 @@
           <t>NODE_S1990_91_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23922,6 +23988,14 @@
         <is>
           <t>NODE_S1989_90_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -23955,6 +24029,8 @@
           <t>NODE_S1990_91_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23969,6 +24045,14 @@
         <is>
           <t>NODE_S1989_90_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -24002,6 +24086,8 @@
           <t>NODE_S1990_91_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24016,6 +24102,14 @@
         <is>
           <t>NODE_S1989_90_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -24049,6 +24143,8 @@
           <t>NODE_S1990_91_0001</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24063,6 +24159,14 @@
         <is>
           <t>NODE_S1989_90_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -24096,6 +24200,8 @@
           <t>NODE_S1990_91_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24110,6 +24216,14 @@
         <is>
           <t>NODE_S1989_90_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -24143,6 +24257,8 @@
           <t>NODE_S1990_91_0007</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24157,6 +24273,14 @@
         <is>
           <t>NODE_S1989_90_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -24190,6 +24314,16 @@
           <t>NODE_S1990_91_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0011</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0010</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24204,6 +24338,14 @@
         <is>
           <t>NODE_S1989_90_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -24284,6 +24426,12 @@
           <t>NODE_S1990_91_0004</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0020</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24298,6 +24446,14 @@
         <is>
           <t>6. kolo: Karviná–Třinec nedohráno a kontumováno 0:5 po vhození láhve. 10. kolo: Karviná–Tábor se nehrálo a bylo kontumováno 0:5.</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -24331,6 +24487,16 @@
           <t>NODE_S1990_91_0004</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0021</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0024</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24345,6 +24511,14 @@
         <is>
           <t>NODE_S1989_90_0020</t>
         </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -24378,6 +24552,12 @@
           <t>NODE_S1990_91_0004</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0023</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24392,6 +24572,14 @@
         <is>
           <t>NODE_S1989_90_0021</t>
         </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -24472,6 +24660,8 @@
           <t>NODE_S1990_91_0004</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24486,6 +24676,14 @@
         <is>
           <t>NODE_S1989_90_0023</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -24519,6 +24717,12 @@
           <t>NODE_S1990_91_0004</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0025</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24533,6 +24737,14 @@
         <is>
           <t>NODE_S1989_90_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -24566,6 +24778,8 @@
           <t>NODE_S1990_91_0004</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24580,6 +24794,14 @@
         <is>
           <t>Šumavan Vimperk po sezóně ukončil činnost, proto sestupoval jen VTJ Racek Pardubice; i ten ukončil činnost a místo podstoupil VTJ Transportě Chrudim.</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -24875,6 +25097,8 @@
           <t>NODE_S1990_91_0029</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24884,6 +25108,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -24959,6 +25191,8 @@
           <t>NODE_S1990_91_0029</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24968,6 +25202,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -25189,6 +25431,12 @@
           <t>NODE_S1990_91_0035</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0041</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25198,6 +25446,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -25231,6 +25487,12 @@
           <t>NODE_S1990_91_0035</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0041</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25240,6 +25502,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -25273,6 +25543,8 @@
           <t>NODE_S1990_91_0035</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25287,6 +25559,14 @@
         <is>
           <t>NODE_S1989_90_0041</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -25320,6 +25600,8 @@
           <t>NODE_S1990_91_0035</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25329,6 +25611,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -25362,6 +25652,8 @@
           <t>NODE_S1990_91_0035</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25371,6 +25663,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -25404,6 +25704,8 @@
           <t>NODE_S1990_91_0035</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25413,6 +25715,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -25582,6 +25892,16 @@
           <t>NODE_S1990_91_0046</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0058</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0057</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25596,6 +25916,14 @@
         <is>
           <t>V maďarském tisku Új Szó jsou u prvních utkání odlišné výsledky; další výsledky ale uváděny nebyly.</t>
         </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -25629,6 +25957,8 @@
           <t>NODE_S1990_91_0046</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25638,6 +25968,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -25671,6 +26009,8 @@
           <t>NODE_S1990_91_0046</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25690,6 +26030,14 @@
         <is>
           <t>NODE_S1989_90_0053</t>
         </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -25817,6 +26165,12 @@
           <t>NODE_S1990_91_0059</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0063</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25826,6 +26180,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -25906,6 +26268,8 @@
           <t>NODE_S1990_91_0059</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25920,6 +26284,14 @@
         <is>
           <t>NODE_S1989_90_0057</t>
         </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -26141,6 +26513,8 @@
           <t>NODE_S1990_91_0059</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26155,6 +26529,14 @@
         <is>
           <t>NODE_S1989_90_0062</t>
         </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -26717,6 +27099,8 @@
           <t>NODE_S1990_91_0075</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26726,6 +27110,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -26759,6 +27151,8 @@
           <t>NODE_S1990_91_0075</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26768,6 +27162,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -26947,6 +27349,12 @@
           <t>NODE_S1990_91_0084</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0087</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26961,6 +27369,14 @@
         <is>
           <t>NODE_S1989_90_0076</t>
         </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -26994,6 +27410,8 @@
           <t>NODE_S1990_91_0084</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27008,6 +27426,14 @@
         <is>
           <t>NODE_S1989_90_0077</t>
         </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="81">
@@ -27214,6 +27640,8 @@
           <t>NODE_S1990_91_0089</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27223,6 +27651,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="86">
@@ -27444,6 +27880,8 @@
           <t>NODE_S1990_91_0093</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27458,6 +27896,14 @@
         <is>
           <t>NODE_S1989_90_0089</t>
         </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -27491,6 +27937,8 @@
           <t>NODE_S1990_91_0093</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27500,6 +27948,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -27763,6 +28219,8 @@
           <t>NODE_S1990_91_0093</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27777,6 +28235,14 @@
         <is>
           <t>NODE_S1989_90_0097</t>
         </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="98">
@@ -27810,6 +28276,8 @@
           <t>NODE_S1990_91_0093</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27819,6 +28287,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="99">
@@ -27852,6 +28328,8 @@
           <t>NODE_S1990_91_0093</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27866,6 +28344,14 @@
         <is>
           <t>NODE_S1989_90_0099</t>
         </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -27899,6 +28385,8 @@
           <t>NODE_S1990_91_0093</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27913,6 +28401,14 @@
         <is>
           <t>NODE_S1989_90_0100</t>
         </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -27946,6 +28442,8 @@
           <t>NODE_S1990_91_0093</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27960,6 +28458,14 @@
         <is>
           <t>NODE_S1989_90_0101</t>
         </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -27993,6 +28499,8 @@
           <t>NODE_S1990_91_0093</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28007,6 +28515,14 @@
         <is>
           <t>NODE_S1989_90_0102</t>
         </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -28134,6 +28650,16 @@
           <t>NODE_S1990_91_0110</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0113</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>NODE_S1990_91_0115</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28148,6 +28674,14 @@
         <is>
           <t>NODE_S1989_90_0106</t>
         </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -28181,6 +28715,8 @@
           <t>NODE_S1990_91_0110</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28195,6 +28731,14 @@
         <is>
           <t>NODE_S1989_90_0107</t>
         </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="107">
@@ -28228,6 +28772,8 @@
           <t>NODE_S1990_91_0110</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28237,6 +28783,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="108">
@@ -28270,6 +28824,8 @@
           <t>NODE_S1990_91_0110</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28284,6 +28840,14 @@
         <is>
           <t>NODE_S1989_90_0108</t>
         </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>7.–9. ZČ</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -28500,6 +29064,8 @@
           <t>NODE_S1990_91_0110</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28509,6 +29075,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="114">
@@ -28699,6 +29273,8 @@
         </is>
       </c>
     </row>
+    <row r="118"/>
+    <row r="119"/>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
@@ -28828,6 +29404,7 @@
         </is>
       </c>
     </row>
+    <row r="127"/>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>

--- a/data/S1990_91_FINAL.xlsx
+++ b/data/S1990_91_FINAL.xlsx
@@ -756,6 +756,11 @@
           <t>HC Dukla Jihlava</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F5" t="n">
         <v>52</v>
       </c>
@@ -23915,8 +23920,6 @@
           <t>NODE_S1990_91_0007</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23972,8 +23975,6 @@
           <t>NODE_S1990_91_0007</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24029,8 +24030,6 @@
           <t>NODE_S1990_91_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24086,8 +24085,6 @@
           <t>NODE_S1990_91_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24143,8 +24140,6 @@
           <t>NODE_S1990_91_0001</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24200,8 +24195,6 @@
           <t>NODE_S1990_91_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24257,8 +24250,6 @@
           <t>NODE_S1990_91_0007</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24431,7 +24422,6 @@
           <t>NODE_S1990_91_0020</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24552,7 +24542,6 @@
           <t>NODE_S1990_91_0004</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>NODE_S1990_91_0023</t>
@@ -24660,8 +24649,6 @@
           <t>NODE_S1990_91_0004</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24717,7 +24704,6 @@
           <t>NODE_S1990_91_0004</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>NODE_S1990_91_0025</t>
@@ -24778,8 +24764,6 @@
           <t>NODE_S1990_91_0004</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25097,8 +25081,6 @@
           <t>NODE_S1990_91_0029</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25191,8 +25173,6 @@
           <t>NODE_S1990_91_0029</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25436,7 +25416,6 @@
           <t>NODE_S1990_91_0041</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25492,7 +25471,6 @@
           <t>NODE_S1990_91_0041</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25543,8 +25521,6 @@
           <t>NODE_S1990_91_0035</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25600,8 +25576,6 @@
           <t>NODE_S1990_91_0035</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25652,8 +25626,6 @@
           <t>NODE_S1990_91_0035</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25704,8 +25676,6 @@
           <t>NODE_S1990_91_0035</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25957,8 +25927,6 @@
           <t>NODE_S1990_91_0046</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26009,8 +25977,6 @@
           <t>NODE_S1990_91_0046</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26165,7 +26131,6 @@
           <t>NODE_S1990_91_0059</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>NODE_S1990_91_0063</t>
@@ -26268,8 +26233,6 @@
           <t>NODE_S1990_91_0059</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26513,8 +26476,6 @@
           <t>NODE_S1990_91_0059</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27099,8 +27060,6 @@
           <t>NODE_S1990_91_0075</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27151,8 +27110,6 @@
           <t>NODE_S1990_91_0075</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27354,7 +27311,6 @@
           <t>NODE_S1990_91_0087</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27410,8 +27366,6 @@
           <t>NODE_S1990_91_0084</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27640,8 +27594,6 @@
           <t>NODE_S1990_91_0089</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27880,8 +27832,6 @@
           <t>NODE_S1990_91_0093</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27937,8 +27887,6 @@
           <t>NODE_S1990_91_0093</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28219,8 +28167,6 @@
           <t>NODE_S1990_91_0093</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28276,8 +28222,6 @@
           <t>NODE_S1990_91_0093</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28328,8 +28272,6 @@
           <t>NODE_S1990_91_0093</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28385,8 +28327,6 @@
           <t>NODE_S1990_91_0093</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28442,8 +28382,6 @@
           <t>NODE_S1990_91_0093</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28499,8 +28437,6 @@
           <t>NODE_S1990_91_0093</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28715,8 +28651,6 @@
           <t>NODE_S1990_91_0110</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28772,8 +28706,6 @@
           <t>NODE_S1990_91_0110</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28824,8 +28756,6 @@
           <t>NODE_S1990_91_0110</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29064,8 +28994,6 @@
           <t>NODE_S1990_91_0110</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29273,8 +29201,6 @@
         </is>
       </c>
     </row>
-    <row r="118"/>
-    <row r="119"/>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
@@ -29404,7 +29330,6 @@
         </is>
       </c>
     </row>
-    <row r="127"/>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
@@ -57682,7 +57607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57934,6 +57859,18 @@
       <c r="B21" t="inlineStr">
         <is>
           <t>Do 2. SNHL postoupili TJ Mostáreň Brezno a VTJ Michalovce "B"; vítěz západoslovenského KP TJ Družstevník Čachtice se postupu vzdal, proto postoupil z 2. místa VS KP TJ Chemko Strážske.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dukla Jihlava</t>
         </is>
       </c>
     </row>

--- a/data/S1990_91_FINAL.xlsx
+++ b/data/S1990_91_FINAL.xlsx
@@ -29201,6 +29201,8 @@
         </is>
       </c>
     </row>
+    <row r="118"/>
+    <row r="119"/>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
@@ -29330,6 +29332,7 @@
         </is>
       </c>
     </row>
+    <row r="127"/>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
